--- a/reports/集团总公司_现金流量表_2025-02.xlsx
+++ b/reports/集团总公司_现金流量表_2025-02.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>171600000</v>
+        <v>170983555</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>343200000</v>
+        <v>342738505</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3544022</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>7074635</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1755291</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>3515361</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>886342</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>1771506</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>702574</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1405022</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>530951</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1062790</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>352137</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>703216</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>264695</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>530449</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>176630</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>352449</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>439798</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>881669</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>222510</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>444064</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>139558</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>279604</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>466400</v>
+        <v>468732</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>932800</v>
+        <v>936398</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3168000</v>
+        <v>3152921</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>6336000</v>
+        <v>6308524</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>175234400</v>
+        <v>183619716</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>105600000</v>
+        <v>105411820</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>211200000</v>
+        <v>211318079</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1179772</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2354100</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>878280</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>1760168</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>590877</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1179916</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>438817</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>878441</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>295352</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>590601</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>220819</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>441380</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>21296000</v>
+        <v>21347398</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>42592000</v>
+        <v>42749505</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>9856000</v>
+        <v>9847229</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>19712000</v>
+        <v>19658007</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>4488000</v>
+        <v>4484739</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>8976000</v>
+        <v>8989410</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>141240000</v>
+        <v>144695103</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>33994400</v>
+        <v>38924613</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>240793</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>480000</v>
+        <v>481981</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2100763</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>4200000</v>
+        <v>4209901</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1281596</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2560000</v>
+        <v>2557323</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2341556</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>20078430</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>40000000</v>
+        <v>40070277</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2886351</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>5800000</v>
+        <v>5782860</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14270987</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>28400000</v>
+        <v>28509178</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>520747</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1040000</v>
+        <v>1043234</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20599177</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18257621</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4680128</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>9400000</v>
+        <v>9379551</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7462640</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>15000000</v>
+        <v>14939232</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7534373</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>15000000</v>
+        <v>15065906</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>239111</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>480000</v>
+        <v>477947</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12381879</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6094385</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>12200000</v>
+        <v>12166322</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6095756</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>12200000</v>
+        <v>12218540</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1002240</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2000000</v>
+        <v>1999761</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>873904</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1740000</v>
+        <v>1744471</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>124381</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>250000</v>
+        <v>249106</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7221006</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5160873</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>21029400</v>
+        <v>25827865</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>21029400</v>
+        <v>25827865</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
